--- a/feedback_forms/007_social_work_introduction_survey--feedback_forms.xlsx
+++ b/feedback_forms/007_social_work_introduction_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'case_management',_'value':_'case_management'}</t>
+          <t>case_management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'case_management', 'value': 'Case Management'}</t>
+          <t>Case Management</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'counseling',_'value':_'counseling'}</t>
+          <t>counseling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'counseling', 'value': 'Counseling'}</t>
+          <t>Counseling</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'support_group',_'value':_'support_group'}</t>
+          <t>support_group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'support_group', 'value': 'Support Group'}</t>
+          <t>Support Group</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'single',_'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'single', 'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'married',_'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'married', 'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'divorced',_'value':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'divorced', 'value': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'widowed',_'value':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'widowed', 'value': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'employed',_'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'employed', 'value': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'student',_'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'student', 'value': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'retired',_'value':_'retired'}</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'retired', 'value': 'Retired'}</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'value': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'pending_review',_'value':_'pending_review'}</t>
+          <t>pending_review</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'pending_review', 'value': 'Pending Review'}</t>
+          <t>Pending Review</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_applicable',_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'not_applicable', 'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending_review',_'value':_'pending_review'}</t>
+          <t>pending_review</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending_review', 'value': 'Pending Review'}</t>
+          <t>Pending Review</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'value': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_applicable',_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'not_applicable', 'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending_review',_'value':_'pending_review'}</t>
+          <t>pending_review</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending_review', 'value': 'Pending Review'}</t>
+          <t>Pending Review</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'value': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_applicable',_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'not_applicable', 'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'value': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'value': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending_review',_'value':_'pending_review'}</t>
+          <t>pending_review</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending_review', 'value': 'Pending Review'}</t>
+          <t>Pending Review</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'value': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_applicable',_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'not_applicable', 'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
